--- a/radeep_custom_rules_iecs.xlsx
+++ b/radeep_custom_rules_iecs.xlsx
@@ -749,12 +749,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[current_date] - 100 years</t>
+          <t>[date_of_birth]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[timestamp]</t>
+          <t>if [patient_status_anual] = '2', [death_date]. Else, [timestamp]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[timestamp]</t>
+          <t>if [patient_status_anual] = '2', [death_date]. Else, [timestamp]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -3068,12 +3068,12 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3105,12 +3105,12 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3167,12 +3167,12 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3294,12 +3294,12 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3376,12 +3376,12 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r1] = '25' or [acute_id_scd_r1] = '27' or [acute_id_scd_r1] = '35' or [acute_id_scd_r1] = '42', or [acute_id_scd_r1] = '44', or [acute_id_scd_r1] = '45', or [acute_id_scd_r1] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5403,12 +5403,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Cannot be empty if [transfusion_status_present] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [transfusion_status_present] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cannot be empty if [regular_transfusion_type] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [regular_transfusion_type] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Cannot be empty if [chelation_treat] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [chelation_treat] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [hydroxiurea_treatment] = '1' / If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>If not empty, branching must be [hydroxiurea_treatment] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cannot be empty if [transplanted] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [transplanted] = '1' / If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -8169,7 +8169,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>test_result_53</t>
+          <t>test_result_31</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Blood film morphology</t>
+          <t>Pyruvate kinase</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>[test_performed_53] = '1'</t>
+          <t>[test_performed_31] = '1'</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_53] = '1'</t>
+          <t>Cannot be empty if [test_performed_31] = '1'</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -8202,27 +8202,27 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>test_result_62</t>
+          <t>test_result_32</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neutrophils result </t>
+          <t>Hexokinase</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>[test_performed_62] = '1'</t>
+          <t>[test_performed_32] = '1'</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_62] = '1'</t>
+          <t>Cannot be empty if [test_performed_32] = '1'</t>
         </is>
       </c>
       <c r="F228" t="inlineStr"/>
@@ -8235,27 +8235,27 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>test_result_63</t>
+          <t>test_result_33</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Lymphocytes result</t>
+          <t>Glucose-6-phosphate dehydrogenase</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>[test_performed_63] = '1'</t>
+          <t>[test_performed_33] = '1'</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_63] = '1'</t>
+          <t>Cannot be empty if [test_performed_33] = '1'</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -8268,27 +8268,27 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>test_result_64</t>
+          <t>test_result_34</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Monocytes result</t>
+          <t>Glucose Phosphate isomerase</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>[test_performed_64] = '1'</t>
+          <t>[test_performed_34] = '1'</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_64] = '1'</t>
+          <t>Cannot be empty if [test_performed_34] = '1'</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -8301,27 +8301,27 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>test_result_65</t>
+          <t>test_result_35</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Eosinophils result</t>
+          <t>Adenosine deaminase</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>[test_performed_65] = '1'</t>
+          <t>[test_performed_35] = '1'</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_65] = '1'</t>
+          <t>Cannot be empty if [test_performed_35] = '1'</t>
         </is>
       </c>
       <c r="F231" t="inlineStr"/>
@@ -8334,27 +8334,27 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>test_result_66</t>
+          <t>test_result_36</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Basophils result</t>
+          <t>Adenylate kinase</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>[test_performed_66] = '1'</t>
+          <t>[test_performed_36] = '1'</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_66] = '1'</t>
+          <t>Cannot be empty if [test_performed_36] = '1'</t>
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
@@ -8367,70 +8367,62 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>test_result_69</t>
+          <t>test_result_37</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>laboratory_tests</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Total iron binding capacity result</t>
+          <t>Aldolase</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>[test_performed_69] = '1'</t>
+          <t>[test_performed_37] = '1'</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_69] = '1' / Value range should be higher than 0 and lower than 1000 / Alert shown if lower than 0 or higher than 1000</t>
+          <t>Cannot be empty if [test_performed_37] = '1'</t>
         </is>
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>record_id</t>
+          <t>test_result_38</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Record ID</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
+          <t>Bisphosphoglycerate mutase</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>[test_performed_38] = '1'</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_38] = '1'</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
@@ -8441,21 +8433,29 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>calc_val</t>
+          <t>test_result_39</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Pseudonym validation</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
+          <t>NADH-cytochrome b5 reductase</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>[test_performed_39] = '1'</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_39] = '1'</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
@@ -8466,27 +8466,27 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>alert_val_id</t>
+          <t>test_result_40</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>&lt;div class='alert alert-danger'&gt;There is a mistake in the format of the pseudonym. Please check the values.&lt;/div&gt;</t>
+          <t>g-Glutamylcysteine synthetase</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>[calc_val]='2'</t>
+          <t>[test_performed_40] = '1'</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [calc_val]='2'</t>
+          <t>Cannot be empty if [test_performed_40] = '1'</t>
         </is>
       </c>
       <c r="F236" t="inlineStr"/>
@@ -8499,17 +8499,29 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>test_result_41</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>patient_registration</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
+          <t>diagnosis</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Gluthathione reductase</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>[test_performed_41] = '1'</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_41] = '1'</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
@@ -8520,27 +8532,27 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>death_cause_other</t>
+          <t>test_result_42</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Other cause of death</t>
+          <t>Glutathione synthetase</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>[cause_of_death] = '998'</t>
+          <t>[test_performed_42] = '1'</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Cannot be empty if [cause_of_death] = '998'</t>
+          <t>Cannot be empty if [test_performed_42] = '1'</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -8553,39 +8565,31 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>date_hcp_contact</t>
+          <t>test_result_43</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>patient_registration</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Date of first contact with HCP</t>
+          <t>Phosphofructokinase</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>[first_hcp_contact] = '1'</t>
+          <t>[test_performed_43] = '1'</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Cannot be empty if [first_hcp_contact] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>[date_of_birth]</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>[timestamp]</t>
-        </is>
-      </c>
+          <t>Cannot be empty if [test_performed_43] = '1'</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
@@ -8594,21 +8598,29 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>test_result_44</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Date of event registration</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
+          <t>Phosphoglycerate kinase</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>[test_performed_44] = '1'</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_44] = '1'</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
@@ -8619,35 +8631,31 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>calc_year_of_immigration</t>
+          <t>test_result_45</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Calc year of immigration</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>Pyrimidine-5'-nucleotidase</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>[test_performed_45] = '1'</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>If not empty, date range must be between [birth_date] and [death_date] or [episode_date]</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>[date_of_birth]</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>[timestamp]</t>
-        </is>
-      </c>
+          <t>Cannot be empty if [test_performed_45] = '1'</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
@@ -8656,27 +8664,27 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>comorbidities_other</t>
+          <t>test_result_46</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Comorbidities other</t>
+          <t>Triosephosphate isomerase</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>[comorbiditiesid(998)] = '1'</t>
+          <t>[test_performed_46] = '1'</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Cannot be empty if [comorbiditiesid(998)] = '1'</t>
+          <t>Cannot be empty if [test_performed_46] = '1'</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -8689,27 +8697,27 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>cm_unknown</t>
+          <t>test_result_47</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Eosin-5-maleimide (EMA) binding test</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>[patient_registrati_arm_1][patient_status] = '1'</t>
+          <t>[test_performed_47] = '1'</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Cannot be empty if [patient_registrati_arm_1][patient_status] = '1'</t>
+          <t>Cannot be empty if [test_performed_47] = '1'</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
@@ -8722,27 +8730,27 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>kg_unknown</t>
+          <t>test_result_48</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weight </t>
+          <t>Ektacytometry</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>[patient_registrati_arm_1][patient_status] = '1'</t>
+          <t>[test_performed_48] = '1'</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Cannot be empty if [patient_registrati_arm_1][patient_status] = '1'</t>
+          <t>Cannot be empty if [test_performed_48] = '1'</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
@@ -8755,17 +8763,29 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>timestamp_label</t>
+          <t>test_result_49</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>annual_update_general_information</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
+          <t>diagnosis</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sodium dodecyl sulfate-polyacrylamide gel electrophoresis (SDS-PAGE) </t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>[test_performed_49] = '1'</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_49] = '1'</t>
+        </is>
+      </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
@@ -8776,7 +8796,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>enter_clin_diag_date</t>
+          <t>test_result_50</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8786,29 +8806,21 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Date of clinical diagnosis:</t>
+          <t>Osmotic Fragility Test or glycerol lysis test</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>[age_date_at_diagnosis] = '4'</t>
+          <t>[test_performed_50] = '1'</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cannot be empty if [age_date_at_diagnosis] = '4' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>[date_of_birth]</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>[timestamp]</t>
-        </is>
-      </c>
+          <t>Cannot be empty if [test_performed_50] = '1'</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
@@ -8817,7 +8829,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>undiagnosed_other_text</t>
+          <t>test_result_51</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8827,17 +8839,17 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Undiagnosed other, specify</t>
+          <t>Hepcidin</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_undiagnosed] = '998'</t>
+          <t>[test_performed_51] = '1'</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_undiagnosed] = '998'</t>
+          <t>Cannot be empty if [test_performed_51] = '1'</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
@@ -8850,7 +8862,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sub_orpha_id_other</t>
+          <t>test_result_52</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -8860,17 +8872,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Sub-diagnosis</t>
+          <t>Bone marrow examination</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '998'</t>
+          <t>[test_performed_52] = '1'</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '998'</t>
+          <t>Cannot be empty if [test_performed_52] = '1'</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
@@ -8883,7 +8895,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>hpo_row_2</t>
+          <t>test_result_53</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -8891,9 +8903,21 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Blood film morphology</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>[test_performed_53] = '1'</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_53] = '1'</t>
+        </is>
+      </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
@@ -8904,17 +8928,29 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>hpo_row_3</t>
+          <t>test_result_62</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
+          <t>laboratory_tests</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neutrophils result </t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>[test_performed_62] = '1'</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_62] = '1'</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
@@ -8925,17 +8961,29 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>hpo_row_4</t>
+          <t>test_result_63</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
+          <t>laboratory_tests</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Lymphocytes result</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>[test_performed_63] = '1'</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_63] = '1'</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
@@ -8946,17 +8994,29 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>hpo_row_5</t>
+          <t>test_result_64</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+          <t>laboratory_tests</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Monocytes result</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>[test_performed_64] = '1'</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Cannot be empty if [test_performed_64] = '1'</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
@@ -8967,27 +9027,27 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>hpoid_table_1</t>
+          <t>test_result_65</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>laboratory_tests</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_1}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Eosinophils result</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '16'</t>
+          <t>[test_performed_65] = '1'</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16'</t>
+          <t>Cannot be empty if [test_performed_65] = '1'</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
@@ -9000,27 +9060,27 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>hpoid_table_2</t>
+          <t>test_result_66</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>laboratory_tests</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_2}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_3}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Basophils result</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '16' and [hpo_row_2(1)] = '1'</t>
+          <t>[test_performed_66] = '1'</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_2(1)] = '1'</t>
+          <t>Cannot be empty if [test_performed_66] = '1'</t>
         </is>
       </c>
       <c r="F254" t="inlineStr"/>
@@ -9033,62 +9093,70 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>hpoid_table_3</t>
+          <t>test_result_69</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>laboratory_tests</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_3}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_4}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Total iron binding capacity result</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '16' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
+          <t>[test_performed_69] = '1'</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
+          <t>Cannot be empty if [test_performed_69] = '1' / Value range should be higher than 0 and lower than 1000 / Alert shown if lower than 0 or higher than 1000</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>hpoid_table_4</t>
+          <t>record_id</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_4}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>[orpha_code_id] = '16' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
+          <t>Record ID</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
@@ -9099,29 +9167,21 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>hpoid_table_5</t>
+          <t>calc_val</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 100%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 100%; text-align: center; height: 18px;"&gt;{hpoid_5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>[orpha_code_id] = '16' and [hpo_row_5(1)] = '1' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_5(1)] = '1' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
-        </is>
-      </c>
+          <t>Pseudonym validation</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
@@ -9132,27 +9192,27 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>new_variation_pklr_a1</t>
+          <t>alert_val_id</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Novel variation PKLR Allele 1</t>
+          <t>&lt;div class='alert alert-danger'&gt;There is a mistake in the format of the pseudonym. Please check the values.&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>[varsid_pklr_a1] = '3150' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[calc_val]='2'</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_pklr_a1] = '3150' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [calc_val]='2'</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -9165,29 +9225,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>new_variation_pklr_a2</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Novel variation PKLR Allele 2</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>[varsid_pklr_a2] = '3150' and [method_of_diagnosis(3)] = '1'</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_pklr_a2] = '3150' and [method_of_diagnosis(3)] = '1'</t>
-        </is>
-      </c>
+          <t>patient_registration</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
@@ -9198,27 +9246,27 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>new_variation_hbb_a1</t>
+          <t>death_cause_other</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Novel variation HBB Allele 1</t>
+          <t>Other cause of death</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>[varsid_hbb_a1] = '3150'</t>
+          <t>[cause_of_death] = '998'</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbb_a1] = '3150'</t>
+          <t>Cannot be empty if [cause_of_death] = '998'</t>
         </is>
       </c>
       <c r="F260" t="inlineStr"/>
@@ -9231,31 +9279,39 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>new_variation_hbb_a2</t>
+          <t>date_hcp_contact</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>patient_registration</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Novel variation HBB Allele 2</t>
+          <t>Date of first contact with HCP</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>[varsid_hbb_a2] = '3150'</t>
+          <t>[first_hcp_contact] = '1'</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbb_a2] = '3150'</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
+          <t>Cannot be empty if [first_hcp_contact] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>[date_of_birth]</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>if [patient_status_anual] = '2', [death_date]. Else, [timestamp]</t>
+        </is>
+      </c>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
@@ -9264,29 +9320,21 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>new_variation_hba1_a1</t>
+          <t>timestamp</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Novel variation HBA1 Allele 1</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>[varsid_hba1_a1] = '3150'</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hba1_a1] = '3150'</t>
-        </is>
-      </c>
+          <t>Date of event registration</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
@@ -9297,31 +9345,35 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>new_variation_hba1_a2</t>
+          <t>calc_year_of_immigration</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Novel variation HBA1 Allele 2</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>[varsid_hba2_a2] = '3150'</t>
-        </is>
-      </c>
+          <t>Calc year of immigration</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hba2_a2] = '3150'</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
+          <t>If [current-instance] = '1', date range must be between [birth_date] and [death_date] or [episode_date]. Else, date range must be between [timestamp] - 1 year and [timestamp]</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>if [current-instance] &gt; '1', [timestamp] - 1 year. Else, [date_of_birth]</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>[timestamp]</t>
+        </is>
+      </c>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
@@ -9330,27 +9382,27 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>new_variation_hba2_a1</t>
+          <t>comorbidities_other</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Novel variation HBA2 Allele 1</t>
+          <t>Comorbidities other</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>[varsid_hba2_a1] = '3150'</t>
+          <t>[comorbiditiesid(998)] = '1'</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hba2_a1] = '3150'</t>
+          <t>Cannot be empty if [comorbiditiesid(998)] = '1'</t>
         </is>
       </c>
       <c r="F264" t="inlineStr"/>
@@ -9363,27 +9415,27 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>new_variation_hba2_a2</t>
+          <t>cm_unknown</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Novel variation HBA2 Allele 2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>[varsid_hba2_a2] = '3150'</t>
+          <t>[patient_registrati_arm_1][patient_status] = '1'</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hba2_a2] = '3150'</t>
+          <t>Cannot be empty if [patient_registrati_arm_1][patient_status] = '1'</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
@@ -9396,27 +9448,27 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>new_variation_hbbp1_a1</t>
+          <t>kg_unknown</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>annual_update_general_information</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Novel variation HBBP1 Allele 1</t>
+          <t xml:space="preserve">Weight </t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>[varsid_hbbp1_a1] = '3150'</t>
+          <t>[patient_registrati_arm_1][patient_status] = '1'</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbbp1_a1] = '3150'</t>
+          <t>Cannot be empty if [patient_registrati_arm_1][patient_status] = '1'</t>
         </is>
       </c>
       <c r="F266" t="inlineStr"/>
@@ -9429,29 +9481,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>new_variation_hbbp1_a2</t>
+          <t>timestamp_label</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>diagnosis</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Novel variation HBBP1 Allele 2</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>[varsid_hbbp1_a2] = '3150'</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbbp1_a2] = '3150'</t>
-        </is>
-      </c>
+          <t>annual_update_general_information</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
@@ -9462,7 +9502,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>new_variation_hbd_a1</t>
+          <t>enter_clin_diag_date</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -9472,21 +9512,29 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Novel variation HBD Allele 1</t>
+          <t>Date of clinical diagnosis:</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>[varsid_hbd_a1] = '3150'</t>
+          <t>[age_date_at_diagnosis] = '4'</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbd_a1] = '3150'</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
+          <t>Cannot be empty if [age_date_at_diagnosis] = '4' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>[date_of_birth]</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>if [patient_status_anual] = '2', [death_date]. Else, [timestamp]</t>
+        </is>
+      </c>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
@@ -9495,7 +9543,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>new_variation_hbd_a2</t>
+          <t>undiagnosed_other_text</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9505,17 +9553,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Novel variation HBD Allele 2</t>
+          <t>Undiagnosed other, specify</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>[varsid_hbd_a2] = '3150'</t>
+          <t>[sub_orpha_id_undiagnosed] = '998'</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbd_a2] = '3150'</t>
+          <t>Cannot be empty if [sub_orpha_id_undiagnosed] = '998'</t>
         </is>
       </c>
       <c r="F269" t="inlineStr"/>
@@ -9528,7 +9576,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>new_variation_hbe1_a1</t>
+          <t>sub_orpha_id_other</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9538,17 +9586,17 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Novel variation HBE1 Allele 1</t>
+          <t>Sub-diagnosis</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>[varsid_hbe1_a1] = '3150'</t>
+          <t>[orpha_code_id] = '998'</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbe1_a1] = '3150'</t>
+          <t>Cannot be empty if [orpha_code_id] = '998'</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -9561,7 +9609,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>new_variation_hbe1_a2</t>
+          <t>hpo_row_2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9569,21 +9617,9 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Novel variation HBE1 Allele 2</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>[varsid_hbe1_a2] = '3150'</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbe1_a2] = '3150'</t>
-        </is>
-      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
@@ -9594,7 +9630,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>new_variation_hbg1_a1</t>
+          <t>hpo_row_3</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9602,21 +9638,9 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Novel variation HBG1 Allele 1</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>[varsid_hbg1_a1] = '3150'</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbg1_a1] = '3150'</t>
-        </is>
-      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
@@ -9627,7 +9651,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>new_variation_hbg1_a2</t>
+          <t>hpo_row_4</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9635,21 +9659,9 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Novel variation HBG1 Allele 2</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>[varsid_hbg1_a2] = '3150'</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbg1_a2] = '3150'</t>
-        </is>
-      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
@@ -9660,7 +9672,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>new_variation_hbg2_a1</t>
+          <t>hpo_row_5</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9668,21 +9680,9 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Novel variation HBG2 Allele 1</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>[varsid_hbg2_a1] = '3150'</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [varsid_hbg2_a1] = '3150'</t>
-        </is>
-      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
@@ -9693,7 +9693,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>new_variation_hbg2_a2</t>
+          <t>hpoid_table_1</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -9703,17 +9703,17 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Novel variation HBG2 Allele 2</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_1}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>[varsid_hbg2_a2] = '3150'</t>
+          <t>[orpha_code_id] = '16'</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbg2_a2] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16'</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
@@ -9726,7 +9726,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>new_variation_hbm_a1</t>
+          <t>hpoid_table_2</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -9736,17 +9736,17 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Novel variation HBM Allele 1</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_2}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_3}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>[varsid_hbm_a1] = '3150'</t>
+          <t>[orpha_code_id] = '16' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbm_a1] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
@@ -9759,7 +9759,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>new_variation_hbm_a2</t>
+          <t>hpoid_table_3</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9769,17 +9769,17 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Novel variation HBM Allele 2</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_3}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_4}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>[varsid_hbm_a1] = '3150'</t>
+          <t>[orpha_code_id] = '16' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbm_a1] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="F277" t="inlineStr"/>
@@ -9792,7 +9792,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>new_variation_hbz_a1</t>
+          <t>hpoid_table_4</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Novel variation HBZ Allele 1</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 87.9066%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;td style="width: 12.0934%; height: 18px;"&gt;Add case (+)&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 87.9066%; text-align: center; height: 18px;"&gt;{hpoid_4}&lt;/td&gt; &lt;td style="width: 12.0934%; text-align: center; height: 18px;"&gt;{hpo_row_5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>[varsid_hbz_a1] = '3150'</t>
+          <t>[orpha_code_id] = '16' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbz_a1] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="F278" t="inlineStr"/>
@@ -9825,7 +9825,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>new_variation_hbz_a2</t>
+          <t>hpoid_table_5</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9835,17 +9835,17 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Novel variation HBZ Allele 2</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 36px;" border="1"&gt; &lt;thead&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 100%; height: 18px;"&gt;How the undiagnosed case is defined ?&lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 100%; text-align: center; height: 18px;"&gt;{hpoid_5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>[varsid_hbz_a2] = '3150'</t>
+          <t>[orpha_code_id] = '16' and [hpo_row_5(1)] = '1' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hbz_a2] = '3150'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '16' and [hpo_row_5(1)] = '1' and [hpo_row_4(1)] = '1' and [hpo_row_3(1)] = '1' and [hpo_row_2(1)] = '1'</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
@@ -9858,7 +9858,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>new_variation_hs40_a1</t>
+          <t>new_variation_pklr_a1</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -9868,17 +9868,17 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Novel variation HS40 Allele 1</t>
+          <t>Novel variation PKLR Allele 1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>[varsid_hs40_a1] = '3150'</t>
+          <t>[varsid_pklr_a1] = '3150' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hs40_a1] = '3150'</t>
+          <t>If not empty, branching must be [varsid_pklr_a1] = '3150' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
@@ -9891,7 +9891,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>new_variation_hs40_a2</t>
+          <t>new_variation_pklr_a2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9901,17 +9901,17 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Novel variation HS40 Allele 2</t>
+          <t>Novel variation PKLR Allele 2</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>[varsid_hs40_a2] = '3150'</t>
+          <t>[varsid_pklr_a2] = '3150' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_hs40_a2] = '3150'</t>
+          <t>If not empty, branching must be [varsid_pklr_a2] = '3150' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F281" t="inlineStr"/>
@@ -9924,7 +9924,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>new_variation_lcrb_a1</t>
+          <t>new_variation_hbb_a1</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9934,17 +9934,17 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Novel variation LCRB Allele 1</t>
+          <t>Novel variation HBB Allele 1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>[varsid_lcrb_a1] = '3150'</t>
+          <t>[varsid_hbb_a1] = '3150'</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_lcrb_a1] = '3150'</t>
+          <t>If not empty, branching must be [varsid_hbb_a1] = '3150'</t>
         </is>
       </c>
       <c r="F282" t="inlineStr"/>
@@ -9957,7 +9957,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>new_variation_lcrb_a2</t>
+          <t>new_variation_hbb_a2</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9967,17 +9967,17 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Novel variation LCRB Allele 2</t>
+          <t>Novel variation HBB Allele 2</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>[varsid_lcrb_a1] = '3150'</t>
+          <t>[varsid_hbb_a2] = '3150'</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_lcrb_a1] = '3150'</t>
+          <t>If not empty, branching must be [varsid_hbb_a2] = '3150'</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -9990,7 +9990,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>new_variation_a3_7hybrid_a1</t>
+          <t>new_variation_hba1_a1</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -10000,17 +10000,17 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Novel variation A3.7 Hybrid Allele 1</t>
+          <t>Novel variation HBA1 Allele 1</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>[varsid_a3_7hybrid_a1] = '3150'</t>
+          <t>[varsid_hba1_a1] = '3150'</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_a3_7hybrid_a1] = '3150'</t>
+          <t>If not empty, branching must be [varsid_hba1_a1] = '3150'</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>new_variation_a3_7hybrid_a2</t>
+          <t>new_variation_hba1_a2</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10033,17 +10033,17 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Novel variation A3.7 Hybrid Allele 2</t>
+          <t>Novel variation HBA1 Allele 2</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>[varsid_a3_7hybrid_a2] = '3150'</t>
+          <t>[varsid_hba2_a2] = '3150'</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [varsid_a3_7hybrid_a2] = '3150'</t>
+          <t>If not empty, branching must be [varsid_hba2_a2] = '3150'</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -10056,7 +10056,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>gene_table</t>
+          <t>new_variation_hba2_a1</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10066,17 +10066,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100.141%; height: 290.188px;" border="1"&gt; &lt;thead&gt; &lt;tr style="height: 38.1875px; background-color: #95a5a6;"&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt;Gene&lt;/td&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt; &lt;p style="text-align: center;"&gt;Allele 2&lt;/p&gt; &lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;PKLR&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_pklr_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_pklr_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;HBB&lt;/td&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;{varsid_hbb_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;{varsid_hbb_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBA1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBA2&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba2_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba2_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBBP1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbbp1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbbp1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBD&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbd_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbd_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBE1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbe1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbe1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBG1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBG2&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg2_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg2_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBM&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbm_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbm_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBZ&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbz_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbz_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HS40&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hs40_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hs40_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;LCRB&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_lcrb_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_lcrb_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;A3.7 Hybrid&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_a3_7hybrid_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_a3_7hybrid_a2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation HBA2 Allele 1</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>[gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hba2_a1] = '3150'</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hba2_a1] = '3150'</t>
         </is>
       </c>
       <c r="F286" t="inlineStr"/>
@@ -10089,7 +10089,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>gene_type_novel</t>
+          <t>new_variation_hba2_a2</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -10099,17 +10099,17 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Novel Gene</t>
+          <t>Novel variation HBA2 Allele 2</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>[gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hba2_a2] = '3150'</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Cannot be empty if [gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hba2_a2] = '3150'</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -10122,7 +10122,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>novelsymbol_r1</t>
+          <t>new_variation_hbbp1_a1</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -10130,15 +10130,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr"/>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Novel variation HBBP1 Allele 1</t>
+        </is>
+      </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>[gene_type_novel] = '1'</t>
+          <t>[varsid_hbbp1_a1] = '3150'</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbbp1_a1] = '3150'</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -10151,7 +10155,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>var_allele2_r1</t>
+          <t>new_variation_hbbp1_a2</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -10159,15 +10163,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Novel variation HBBP1 Allele 2</t>
+        </is>
+      </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>[gene_type_novel] = '1'</t>
+          <t>[varsid_hbbp1_a2] = '3150'</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbbp1_a2] = '3150'</t>
         </is>
       </c>
       <c r="F289" t="inlineStr"/>
@@ -10180,7 +10188,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>var_allele1_r1</t>
+          <t>new_variation_hbd_a1</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -10188,15 +10196,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Novel variation HBD Allele 1</t>
+        </is>
+      </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>[gene_type_novel] = '1'</t>
+          <t>[varsid_hbd_a1] = '3150'</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbd_a1] = '3150'</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
@@ -10209,7 +10221,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>new_novel_row2</t>
+          <t>new_variation_hbd_a2</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -10217,9 +10229,21 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Novel variation HBD Allele 2</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>[varsid_hbd_a2] = '3150'</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>If not empty, branching must be [varsid_hbd_a2] = '3150'</t>
+        </is>
+      </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
@@ -10230,7 +10254,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>novel_gene_r1</t>
+          <t>new_variation_hbe1_a1</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -10240,17 +10264,17 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; Add new row&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r1}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r1}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r1}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation HBE1 Allele 1</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>[gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hbe1_a1] = '3150'</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbe1_a1] = '3150'</t>
         </is>
       </c>
       <c r="F292" t="inlineStr"/>
@@ -10263,7 +10287,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>var_allele2_r2</t>
+          <t>new_variation_hbe1_a2</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -10271,15 +10295,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Novel variation HBE1 Allele 2</t>
+        </is>
+      </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hbe1_a2] = '3150'</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbe1_a2] = '3150'</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
@@ -10292,7 +10320,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>novelsymbol_r2</t>
+          <t>new_variation_hbg1_a1</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -10300,15 +10328,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Novel variation HBG1 Allele 1</t>
+        </is>
+      </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hbg1_a1] = '3150'</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbg1_a1] = '3150'</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
@@ -10321,7 +10353,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>var_allele1_r2</t>
+          <t>new_variation_hbg1_a2</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -10329,15 +10361,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Novel variation HBG1 Allele 2</t>
+        </is>
+      </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hbg1_a2] = '3150'</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbg1_a2] = '3150'</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
@@ -10350,7 +10386,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>new_novel_row3</t>
+          <t>new_variation_hbg2_a1</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -10358,9 +10394,21 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Novel variation HBG2 Allele 1</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>[varsid_hbg2_a1] = '3150'</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>If not empty, branching must be [varsid_hbg2_a1] = '3150'</t>
+        </is>
+      </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
@@ -10371,7 +10419,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>novel_gene_r2</t>
+          <t>new_variation_hbg2_a2</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -10381,17 +10429,17 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r2}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r2}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r2}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row3}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation HBG2 Allele 2</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hbg2_a2] = '3150'</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbg2_a2] = '3150'</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -10404,7 +10452,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>new_novel_row4</t>
+          <t>new_variation_hbm_a1</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -10412,9 +10460,21 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Novel variation HBM Allele 1</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>[varsid_hbm_a1] = '3150'</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>If not empty, branching must be [varsid_hbm_a1] = '3150'</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
@@ -10425,7 +10485,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>novelsymbol_r3</t>
+          <t>new_variation_hbm_a2</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -10433,15 +10493,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Novel variation HBM Allele 2</t>
+        </is>
+      </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hbm_a1] = '3150'</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbm_a1] = '3150'</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -10454,7 +10518,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>var_allele1_r3</t>
+          <t>new_variation_hbz_a1</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10462,15 +10526,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Novel variation HBZ Allele 1</t>
+        </is>
+      </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hbz_a1] = '3150'</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbz_a1] = '3150'</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -10483,7 +10551,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>var_allele2_r3</t>
+          <t>new_variation_hbz_a2</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -10491,15 +10559,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Novel variation HBZ Allele 2</t>
+        </is>
+      </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hbz_a2] = '3150'</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hbz_a2] = '3150'</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -10512,7 +10584,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>novel_gene_r3</t>
+          <t>new_variation_hs40_a1</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -10522,17 +10594,17 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r3}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r3}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r3}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row4}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation HS40 Allele 1</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_hs40_a1] = '3150'</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_hs40_a1] = '3150'</t>
         </is>
       </c>
       <c r="F302" t="inlineStr"/>
@@ -10545,7 +10617,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>var_allele1_r4</t>
+          <t>new_variation_hs40_a2</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10553,15 +10625,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Novel variation HS40 Allele 2</t>
+        </is>
+      </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_hs40_a2] = '3150'</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_hs40_a2] = '3150'</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
@@ -10574,7 +10650,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>var_allele2_r4</t>
+          <t>new_variation_lcrb_a1</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -10582,15 +10658,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Novel variation LCRB Allele 1</t>
+        </is>
+      </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_lcrb_a1] = '3150'</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_lcrb_a1] = '3150'</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
@@ -10603,7 +10683,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>novelsymbol_r4</t>
+          <t>new_variation_lcrb_a2</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -10611,15 +10691,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Novel variation LCRB Allele 2</t>
+        </is>
+      </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[varsid_lcrb_a1] = '3150'</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [varsid_lcrb_a1] = '3150'</t>
         </is>
       </c>
       <c r="F305" t="inlineStr"/>
@@ -10632,7 +10716,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>new_novel_row5</t>
+          <t>new_variation_a3_7hybrid_a1</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -10640,9 +10724,21 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr"/>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Novel variation A3.7 Hybrid Allele 1</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>[varsid_a3_7hybrid_a1] = '3150'</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>If not empty, branching must be [varsid_a3_7hybrid_a1] = '3150'</t>
+        </is>
+      </c>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
@@ -10653,7 +10749,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>novel_gene_r4</t>
+          <t>new_variation_a3_7hybrid_a2</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -10663,17 +10759,17 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r4}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r4}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r4}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+          <t>Novel variation A3.7 Hybrid Allele 2</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[varsid_a3_7hybrid_a2] = '3150'</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [varsid_a3_7hybrid_a2] = '3150'</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
@@ -10686,7 +10782,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>var_allele1_r5</t>
+          <t>gene_table</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -10694,15 +10790,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100.141%; height: 290.188px;" border="1"&gt; &lt;thead&gt; &lt;tr style="height: 38.1875px; background-color: #95a5a6;"&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt;Gene&lt;/td&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 38.1875px; text-align: center;"&gt; &lt;p style="text-align: center;"&gt;Allele 2&lt;/p&gt; &lt;/td&gt; &lt;/tr&gt; &lt;/thead&gt; &lt;tbody&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;PKLR&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_pklr_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_pklr_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;HBB&lt;/td&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;{varsid_hbb_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; text-align: center; height: 18px;"&gt;{varsid_hbb_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBA1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBA2&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba2_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hba2_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBBP1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbbp1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbbp1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBD&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbd_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbd_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBE1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbe1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbe1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBG1&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg1_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg1_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBG2&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg2_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbg2_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBM&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbm_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbm_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HBZ&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbz_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hbz_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;HS40&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hs40_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_hs40_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;LCRB&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_lcrb_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_lcrb_a2}&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 18px;"&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;A3.7 Hybrid&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_a3_7hybrid_a1}&lt;/td&gt; &lt;td style="width: 33.2861%; height: 18px; text-align: center;"&gt;{varsid_a3_7hybrid_a2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>If not empty, branching must be [gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -10715,7 +10815,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>var_allele2_r5</t>
+          <t>gene_type_novel</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10723,15 +10823,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Novel Gene</t>
+        </is>
+      </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>[gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
+          <t>Cannot be empty if [gene_type(1)] = '0' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -10744,7 +10848,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>novelsymbol_r5</t>
+          <t>novelsymbol_r1</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -10755,12 +10859,12 @@
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
@@ -10773,7 +10877,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>novel_gene_r5</t>
+          <t>var_allele2_r1</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10781,19 +10885,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 26.9122%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 38.3853%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 34.7025%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 26.9122%; height: 42px; text-align: center;"&gt;{novelsymbol_r5}&lt;/td&gt; &lt;td style="width: 38.3853%; height: 42px; text-align: center;"&gt;{var_allele1_r5}&lt;/td&gt; &lt;td style="width: 34.7025%; height: 42px; text-align: center;"&gt;{var_allele2_r5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
-        </is>
-      </c>
+      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1'  and [method_of_diagnosis(3)] = '1' and [gene_type_novel] = '1'</t>
+          <t>[gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1'  and [method_of_diagnosis(3)] = '1' and [gene_type_novel] = '1'</t>
+          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
@@ -10806,7 +10906,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>enter_onset_date</t>
+          <t>var_allele1_r1</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -10814,31 +10914,19 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
+      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>[age_onset] = '3'</t>
+          <t>[gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Cannot be empty if [age_onset] = '3' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>[date_of_birth]</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>[timestamp]</t>
-        </is>
-      </c>
+          <t>If not empty, branching must be [gene_type_novel] = '1'</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
@@ -10847,7 +10935,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>reason_diag_other</t>
+          <t>new_novel_row2</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10855,21 +10943,9 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Other, specify:</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>[reason_diagnosis] = '998'</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [reason_diagnosis] = '998'</t>
-        </is>
-      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr"/>
@@ -10880,7 +10956,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>fsymptoms_other</t>
+          <t>novel_gene_r1</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10890,17 +10966,17 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Other, specify:</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; Add new row&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r1}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r1}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r1}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row2}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>[fsymptoms_id(998)] = '1'</t>
+          <t>[gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [fsymptoms_id(998)] = '1'</t>
+          <t>If not empty, branching must be [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -10913,7 +10989,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>neonatal_jaundice</t>
+          <t>var_allele2_r2</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -10921,19 +10997,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Did the patient show neonatal jaundice?</t>
-        </is>
-      </c>
+      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>[age_onset] = '1' or [age_onset] = '2'</t>
+          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
@@ -10946,7 +11018,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>require_phototherapy</t>
+          <t>novelsymbol_r2</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -10954,19 +11026,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Did the patient require phototherapy?</t>
-        </is>
-      </c>
+      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>[neonatal_jaundice] = '1'</t>
+          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [neonatal_jaundice] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -10979,7 +11047,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>neonatal_haemolytic_anemia</t>
+          <t>var_allele1_r2</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -10987,19 +11055,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Did the patient show neonatal hemolytic anemia?</t>
-        </is>
-      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>[age_onset] = '1' or [age_onset] = '2'</t>
+          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -11012,7 +11076,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>requiring_blood_transfusion</t>
+          <t>new_novel_row3</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -11020,21 +11084,9 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Did the patient require blood transfusion?</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>[neonatal_haemolytic_anemia] = '1'</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>If not empty, branching must be [neonatal_haemolytic_anemia] = '1'</t>
-        </is>
-      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr"/>
@@ -11045,7 +11097,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>other_neonatal</t>
+          <t>novel_gene_r2</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -11055,17 +11107,17 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Other severe complications in the neonatal period:</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r2}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r2}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r2}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row3}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>[age_onset] = '1' or [age_onset] = '2'</t>
+          <t>[new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
@@ -11078,7 +11130,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>test_performed_12</t>
+          <t>new_novel_row4</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -11086,21 +11138,9 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hemoglobin F performed </t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5' or [orpha_code_id] = '13'</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5' or [orpha_code_id] = '13'</t>
-        </is>
-      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr"/>
       <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr"/>
@@ -11111,7 +11151,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>test_performed_14</t>
+          <t>novelsymbol_r3</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -11119,19 +11159,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hemoglobin A2 in diagnosis performed </t>
-        </is>
-      </c>
+      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5'</t>
+          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5'</t>
+          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
@@ -11144,7 +11180,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>test_result_14</t>
+          <t>var_allele1_r3</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -11152,19 +11188,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Hemoglobin A2 in diagnosis (%)</t>
-        </is>
-      </c>
+      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>[test_performed_14] = '1'</t>
+          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_14] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F322" t="inlineStr"/>
@@ -11177,7 +11209,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>test_performed_15</t>
+          <t>var_allele2_r3</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -11185,19 +11217,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abnormal Hemoglobin Fraction performed </t>
-        </is>
-      </c>
+      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '6' or [orpha_code_id] = '7' or [orpha_code_id] = '8' or [orpha_code_id] = '15' or [orpha_code_id] = '13'</t>
+          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '6' or [orpha_code_id] = '7' or [orpha_code_id] = '8' or [orpha_code_id] = '15' or [orpha_code_id] = '13'</t>
+          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F323" t="inlineStr"/>
@@ -11210,7 +11238,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>test_performed_16</t>
+          <t>novel_gene_r3</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -11220,17 +11248,17 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>p50 performed</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r3}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r3}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r3}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row4}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '8' or [sub_orpha_id_undiagnosed] = '2'</t>
+          <t>[new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '8' or [sub_orpha_id_undiagnosed] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F324" t="inlineStr"/>
@@ -11243,7 +11271,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>test_result_16</t>
+          <t>var_allele1_r4</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -11251,19 +11279,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>p50 (mmHg)</t>
-        </is>
-      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>([orpha_code_id] = '8' or ([orpha_code_id] = '16'  and [sub_orpha_id_undiagnosed] = '2')) and [test_performed_16] = '1'</t>
+          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>If not empty, branching must be ([orpha_code_id] = '8' or ([orpha_code_id] = '16'  and [sub_orpha_id_undiagnosed] = '2')) and [test_performed_16] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -11276,7 +11300,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>test_performed_17</t>
+          <t>var_allele2_r4</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -11284,19 +11308,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Unstable Hemoglobin test performed</t>
-        </is>
-      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '15' or [sub_orpha_id_undiagnosed] = '2'</t>
+          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [orpha_code_id] = '15' or [sub_orpha_id_undiagnosed] = '2'</t>
+          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -11309,7 +11329,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>test_result_17</t>
+          <t>novelsymbol_r4</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -11317,19 +11337,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Unstable Hemoglobin test</t>
-        </is>
-      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>[test_performed_17] = '1'</t>
+          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>If not empty, branching must be [test_performed_17] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
@@ -11342,7 +11358,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>test_performed_31</t>
+          <t>new_novel_row5</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -11350,21 +11366,9 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Pyruvate kinase performed</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
-        </is>
-      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr"/>
@@ -11375,7 +11379,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>test_result_31</t>
+          <t>novel_gene_r4</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -11385,17 +11389,17 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Pyruvate kinase</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 22.0963%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 31.4301%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 28.4849%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;td style="width: 17.847%; text-align: center; height: 18px;"&gt; +&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 22.0963%; height: 42px; text-align: center;"&gt;{novelsymbol_r4}&lt;/td&gt; &lt;td style="width: 31.4301%; height: 42px; text-align: center;"&gt;{var_allele1_r4}&lt;/td&gt; &lt;td style="width: 28.4849%; height: 42px; text-align: center;"&gt;{var_allele2_r4}&lt;/td&gt; &lt;td style="width: 17.847%; height: 42px; text-align: center;"&gt;{new_novel_row5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>[test_performed_31] = '1'</t>
+          <t>[new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_31] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -11408,7 +11412,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>test_performed_32</t>
+          <t>var_allele1_r5</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -11416,19 +11420,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Hexokinase performed</t>
-        </is>
-      </c>
+      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
+          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
+          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -11441,7 +11441,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>test_result_32</t>
+          <t>var_allele2_r5</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11449,19 +11449,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Hexokinase</t>
-        </is>
-      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>[test_performed_32] = '1'</t>
+          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_32] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [method_of_diagnosis(3)] = '1'</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
@@ -11474,7 +11470,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>test_performed_33</t>
+          <t>novelsymbol_r5</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11482,19 +11478,15 @@
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Glucose-6-phosphate dehydrogenase performed</t>
-        </is>
-      </c>
+      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
+          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
+          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
@@ -11507,7 +11499,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>test_result_33</t>
+          <t>novel_gene_r5</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -11517,17 +11509,17 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Glucose-6-phosphate dehydrogenase</t>
+          <t>&lt;div class="rich-text-field-label"&gt;&lt;table style="border-collapse: collapse; width: 100%; height: 60px;" border="1"&gt; &lt;tbody&gt; &lt;tr style="background-color: #95a5a6; height: 18px;"&gt; &lt;td style="width: 26.9122%; text-align: center; height: 18px;"&gt;Gene&lt;/td&gt; &lt;td style="width: 38.3853%; text-align: center; height: 18px;"&gt;Allele 1&lt;/td&gt; &lt;td style="width: 34.7025%; text-align: center; height: 18px;"&gt;Allele 2&lt;/td&gt; &lt;/tr&gt; &lt;tr style="height: 42px;"&gt; &lt;td style="width: 26.9122%; height: 42px; text-align: center;"&gt;{novelsymbol_r5}&lt;/td&gt; &lt;td style="width: 38.3853%; height: 42px; text-align: center;"&gt;{var_allele1_r5}&lt;/td&gt; &lt;td style="width: 34.7025%; height: 42px; text-align: center;"&gt;{var_allele2_r5}&lt;/td&gt; &lt;/tr&gt; &lt;/tbody&gt; &lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>[test_performed_33] = '1'</t>
+          <t>[new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1'  and [method_of_diagnosis(3)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_33] = '1'</t>
+          <t>If not empty, branching must be [new_novel_row5(1)] = '1' and [new_novel_row4(1)] = '1' and [new_novel_row3(1)] = '1' and [new_novel_row2(1)] = '1'  and [method_of_diagnosis(3)] = '1' and [gene_type_novel] = '1'</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
@@ -11540,7 +11532,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>test_performed_34</t>
+          <t>enter_onset_date</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -11550,21 +11542,29 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Glucose Phosphate isomerase performed</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '11'</t>
+          <t>[age_onset] = '3'</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '11'</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
+          <t>Cannot be empty if [age_onset] = '3' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>[date_of_birth]</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>if [patient_status_anual] = '2', [death_date]. Else, [timestamp]</t>
+        </is>
+      </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
@@ -11573,7 +11573,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>test_result_34</t>
+          <t>reason_diag_other</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -11583,17 +11583,17 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Glucose Phosphate isomerase</t>
+          <t>Other, specify:</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>[test_performed_34] = '1'</t>
+          <t>[reason_diagnosis] = '998'</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_34] = '1'</t>
+          <t>If not empty, branching must be [reason_diagnosis] = '998'</t>
         </is>
       </c>
       <c r="F335" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>test_performed_35</t>
+          <t>fsymptoms_other</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11616,17 +11616,17 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Adenosine deaminase performed</t>
+          <t>Other, specify:</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '18'</t>
+          <t>[fsymptoms_id(998)] = '1'</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '18'</t>
+          <t>If not empty, branching must be [fsymptoms_id(998)] = '1'</t>
         </is>
       </c>
       <c r="F336" t="inlineStr"/>
@@ -11639,7 +11639,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>test_result_35</t>
+          <t>neonatal_jaundice</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -11649,17 +11649,17 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Adenosine deaminase</t>
+          <t>Did the patient show neonatal jaundice?</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>[test_performed_35] = '1'</t>
+          <t>[age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_35] = '1'</t>
+          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="F337" t="inlineStr"/>
@@ -11672,7 +11672,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>test_performed_36</t>
+          <t>require_phototherapy</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -11682,17 +11682,17 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Adenylate kinase performed</t>
+          <t>Did the patient require phototherapy?</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '17'</t>
+          <t>[neonatal_jaundice] = '1'</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '17'</t>
+          <t>If not empty, branching must be [neonatal_jaundice] = '1'</t>
         </is>
       </c>
       <c r="F338" t="inlineStr"/>
@@ -11705,7 +11705,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>test_result_36</t>
+          <t>neonatal_haemolytic_anemia</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -11715,17 +11715,17 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Adenylate kinase</t>
+          <t>Did the patient show neonatal hemolytic anemia?</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>[test_performed_36] = '1'</t>
+          <t>[age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_36] = '1'</t>
+          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="F339" t="inlineStr"/>
@@ -11738,7 +11738,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>test_performed_37</t>
+          <t>requiring_blood_transfusion</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -11748,17 +11748,17 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Aldolase performed</t>
+          <t>Did the patient require blood transfusion?</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '8'</t>
+          <t>[neonatal_haemolytic_anemia] = '1'</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '8'</t>
+          <t>If not empty, branching must be [neonatal_haemolytic_anemia] = '1'</t>
         </is>
       </c>
       <c r="F340" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>test_result_37</t>
+          <t>other_neonatal</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Aldolase</t>
+          <t>Other severe complications in the neonatal period:</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>[test_performed_37] = '1'</t>
+          <t>[age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_37] = '1'</t>
+          <t>If not empty, branching must be [age_onset] = '1' or [age_onset] = '2'</t>
         </is>
       </c>
       <c r="F341" t="inlineStr"/>
@@ -11804,7 +11804,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>test_performed_38</t>
+          <t>test_performed_12</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -11814,17 +11814,17 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bisphosphoglycerate mutase performed</t>
+          <t xml:space="preserve">Hemoglobin F performed </t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '12'</t>
+          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5' or [orpha_code_id] = '13'</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '12'</t>
+          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5' or [orpha_code_id] = '13'</t>
         </is>
       </c>
       <c r="F342" t="inlineStr"/>
@@ -11837,7 +11837,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>test_result_38</t>
+          <t>test_performed_14</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -11847,17 +11847,17 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bisphosphoglycerate mutase</t>
+          <t xml:space="preserve">Hemoglobin A2 in diagnosis performed </t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>[test_performed_38] = '1'</t>
+          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_38] = '1'</t>
+          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="F343" t="inlineStr"/>
@@ -11870,7 +11870,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>test_performed_39</t>
+          <t>test_result_14</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>NADH-cytochrome b5 reductase performed</t>
+          <t>Hemoglobin A2 in diagnosis (%)</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '9'</t>
+          <t>[test_performed_14] = '1'</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '9'</t>
+          <t>Cannot be empty if [test_performed_14] = '1'</t>
         </is>
       </c>
       <c r="F344" t="inlineStr"/>
@@ -11903,7 +11903,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>test_result_39</t>
+          <t>test_performed_15</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -11913,17 +11913,17 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>NADH-cytochrome b5 reductase</t>
+          <t xml:space="preserve">Abnormal Hemoglobin Fraction performed </t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>[test_performed_39] = '1'</t>
+          <t>[orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '6' or [orpha_code_id] = '7' or [orpha_code_id] = '8' or [orpha_code_id] = '15' or [orpha_code_id] = '13'</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_39] = '1'</t>
+          <t>Cannot be empty if [orpha_code_id] = '1' or [orpha_code_id] = '2' or [orpha_code_id] = '6' or [orpha_code_id] = '7' or [orpha_code_id] = '8' or [orpha_code_id] = '15' or [orpha_code_id] = '13'</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
@@ -11936,7 +11936,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>test_performed_40</t>
+          <t>test_performed_16</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -11946,17 +11946,17 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>g-Glutamylcysteine synthetase performed</t>
+          <t>p50 performed</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '3'</t>
+          <t>[orpha_code_id] = '8' or [sub_orpha_id_undiagnosed] = '2'</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '3'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '8' or [sub_orpha_id_undiagnosed] = '2'</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -11969,7 +11969,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>test_result_40</t>
+          <t>test_result_16</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -11979,17 +11979,17 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>g-Glutamylcysteine synthetase</t>
+          <t>p50 (mmHg)</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>[test_performed_40] = '1'</t>
+          <t>([orpha_code_id] = '8' or ([orpha_code_id] = '16'  and [sub_orpha_id_undiagnosed] = '2')) and [test_performed_16] = '1'</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_40] = '1'</t>
+          <t>If not empty, branching must be ([orpha_code_id] = '8' or ([orpha_code_id] = '16'  and [sub_orpha_id_undiagnosed] = '2')) and [test_performed_16] = '1'</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
@@ -12002,7 +12002,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>test_performed_41</t>
+          <t>test_performed_17</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -12012,17 +12012,17 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Gluthathione reductase performed</t>
+          <t>Unstable Hemoglobin test performed</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '4'</t>
+          <t>[orpha_code_id] = '15' or [sub_orpha_id_undiagnosed] = '2'</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '4'</t>
+          <t>If not empty, branching must be [orpha_code_id] = '15' or [sub_orpha_id_undiagnosed] = '2'</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
@@ -12035,7 +12035,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>test_result_41</t>
+          <t>test_result_17</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -12045,17 +12045,17 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Gluthathione reductase</t>
+          <t>Unstable Hemoglobin test</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>[test_performed_41] = '1'</t>
+          <t>[test_performed_17] = '1'</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_41] = '1'</t>
+          <t>If not empty, branching must be [test_performed_17] = '1'</t>
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
@@ -12068,7 +12068,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>test_performed_42</t>
+          <t>test_performed_31</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -12078,17 +12078,17 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Glutathione synthetase performed</t>
+          <t>Pyruvate kinase performed</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '2'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '2'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
@@ -12101,7 +12101,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>test_result_42</t>
+          <t>test_performed_32</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -12111,17 +12111,17 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Glutathione synthetase</t>
+          <t>Hexokinase performed</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>[test_performed_42] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_42] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="F351" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>test_performed_43</t>
+          <t>test_performed_33</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -12144,17 +12144,17 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Phosphofructokinase performed</t>
+          <t>Glucose-6-phosphate dehydrogenase performed</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '6'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '6'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '10' or [sub_orpha_id_rare_enzyme] = '13' or [sub_orpha_id_rare_enzyme] = '15'</t>
         </is>
       </c>
       <c r="F352" t="inlineStr"/>
@@ -12167,7 +12167,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>test_result_43</t>
+          <t>test_performed_34</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -12177,17 +12177,17 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Phosphofructokinase</t>
+          <t>Glucose Phosphate isomerase performed</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>[test_performed_43] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '11'</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_43] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '11'</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
@@ -12200,7 +12200,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>test_performed_44</t>
+          <t>test_performed_35</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -12210,17 +12210,17 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Phosphoglycerate kinase performed</t>
+          <t>Adenosine deaminase performed</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '9'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '18'</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '9'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '18'</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -12233,7 +12233,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>test_result_44</t>
+          <t>test_performed_36</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -12243,17 +12243,17 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Phosphoglycerate kinase</t>
+          <t>Adenylate kinase performed</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>[test_performed_44] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '17'</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_44] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '17'</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -12266,7 +12266,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>test_performed_45</t>
+          <t>test_performed_37</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -12276,17 +12276,17 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Pyrimidine-5'-nucleotidase performed</t>
+          <t>Aldolase performed</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '16'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '8'</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '16'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '8'</t>
         </is>
       </c>
       <c r="F356" t="inlineStr"/>
@@ -12299,7 +12299,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>test_result_45</t>
+          <t>test_performed_38</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -12309,17 +12309,17 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Pyrimidine-5'-nucleotidase</t>
+          <t>Bisphosphoglycerate mutase performed</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>[test_performed_45] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '12'</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_45] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '12'</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -12332,7 +12332,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>test_performed_46</t>
+          <t>test_performed_39</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -12342,17 +12342,17 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Triosephosphate isomerase performed</t>
+          <t>NADH-cytochrome b5 reductase performed</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_enzyme] = '7'</t>
+          <t>[orpha_code_id] = '9'</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '7'</t>
+          <t>Cannot be empty if [orpha_code_id] = '9'</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -12365,7 +12365,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>test_result_46</t>
+          <t>test_performed_40</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -12375,17 +12375,17 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Triosephosphate isomerase</t>
+          <t>g-Glutamylcysteine synthetase performed</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>[test_performed_46] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '3'</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_46] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '3'</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -12398,7 +12398,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>test_performed_47</t>
+          <t>test_performed_41</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -12408,17 +12408,17 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Eosin-5-maleimide (EMA) binding test performed</t>
+          <t>Gluthathione reductase performed</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '4'</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '4'</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
@@ -12431,7 +12431,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>test_result_47</t>
+          <t>test_performed_42</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -12441,17 +12441,17 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Eosin-5-maleimide (EMA) binding test</t>
+          <t>Glutathione synthetase performed</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>[test_performed_47] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '2'</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_47] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '2'</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
@@ -12464,7 +12464,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>test_performed_48</t>
+          <t>test_performed_43</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -12474,17 +12474,17 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Ektacytometry performed</t>
+          <t>Phosphofructokinase performed</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '6'</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '6'</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
@@ -12497,7 +12497,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>test_result_48</t>
+          <t>test_performed_44</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -12507,17 +12507,17 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Ektacytometry</t>
+          <t>Phosphoglycerate kinase performed</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>[test_performed_48] = '1'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '9'</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_48] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '9'</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
@@ -12530,7 +12530,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>test_result_48_other</t>
+          <t>test_performed_45</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -12540,17 +12540,17 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other, specify </t>
+          <t>Pyrimidine-5'-nucleotidase performed</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>[test_result_48] = '8'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '16'</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_result_48] = '8'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '16'</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
@@ -12563,7 +12563,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>test_performed_49</t>
+          <t>test_performed_46</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -12573,17 +12573,17 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Sodium dodecyl sulfate-polyacrylamide gel electrophoresis (SDS-PAGE)  performed</t>
+          <t>Triosephosphate isomerase performed</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
+          <t>[sub_orpha_id_rare_enzyme] = '7'</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_enzyme] = '7'</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
@@ -12596,7 +12596,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>test_result_49</t>
+          <t>test_performed_47</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -12606,17 +12606,17 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sodium dodecyl sulfate-polyacrylamide gel electrophoresis (SDS-PAGE) </t>
+          <t>Eosin-5-maleimide (EMA) binding test performed</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>[test_performed_49] = '1'</t>
+          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_49] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
@@ -12629,7 +12629,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>test_result_49_other</t>
+          <t>test_performed_48</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12639,17 +12639,17 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other, specify </t>
+          <t>Ektacytometry performed</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>[test_result_49] = '8'</t>
+          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_result_49] = '8'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="F367" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>test_performed_50</t>
+          <t>test_result_48_other</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -12672,17 +12672,17 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Osmotic Fragility Test or glycerol lysis test performed</t>
+          <t xml:space="preserve">Other, specify </t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
+          <t>[test_result_48] = '8'</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [test_result_48] = '8'</t>
         </is>
       </c>
       <c r="F368" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>test_result_50</t>
+          <t>test_performed_49</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Osmotic Fragility Test or glycerol lysis test</t>
+          <t>Sodium dodecyl sulfate-polyacrylamide gel electrophoresis (SDS-PAGE)  performed</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>[test_performed_50] = '1'</t>
+          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_50] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="F369" t="inlineStr"/>
@@ -12728,7 +12728,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>test_performed_51</t>
+          <t>test_result_49_other</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -12738,17 +12738,17 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Hepcidin performed</t>
+          <t xml:space="preserve">Other, specify </t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '14' or [orpha_code_id] = '3'</t>
+          <t>[test_result_49] = '8'</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '14' or [orpha_code_id] = '3'</t>
+          <t>Cannot be empty if [test_result_49] = '8'</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -12761,7 +12761,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>test_result_51</t>
+          <t>test_performed_50</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -12771,17 +12771,17 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Hepcidin</t>
+          <t>Osmotic Fragility Test or glycerol lysis test performed</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>[test_performed_51] = '1'</t>
+          <t>[sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_51] = '1'</t>
+          <t>Cannot be empty if [sub_orpha_id_rare_membrane] = '1' or [sub_orpha_id_rare_membrane] = '2' or [sub_orpha_id_rare_membrane] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -12794,7 +12794,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>test_performed_52</t>
+          <t>test_performed_51</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -12804,17 +12804,17 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Bone marrow examination performed</t>
+          <t>Hepcidin performed</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>[orpha_code_id] = '14' or [orpha_code_id] = '3' or [orpha_code_id] = '5'</t>
+          <t>[orpha_code_id] = '14' or [orpha_code_id] = '3'</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Cannot be empty if [orpha_code_id] = '14' or [orpha_code_id] = '3' or [orpha_code_id] = '5'</t>
+          <t>Cannot be empty if [orpha_code_id] = '14' or [orpha_code_id] = '3'</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
@@ -12827,7 +12827,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>test_result_52</t>
+          <t>test_performed_52</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -12837,17 +12837,17 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Bone marrow examination</t>
+          <t>Bone marrow examination performed</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>[test_performed_52] = '1'</t>
+          <t>[orpha_code_id] = '14' or [orpha_code_id] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Cannot be empty if [test_performed_52] = '1'</t>
+          <t>Cannot be empty if [orpha_code_id] = '14' or [orpha_code_id] = '3' or [orpha_code_id] = '5'</t>
         </is>
       </c>
       <c r="F373" t="inlineStr"/>
@@ -15608,12 +15608,12 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications] = '1' / If [acute_id_r1] = '9' or [acute_id_r1] = '18' or [acute_id_r1] = '20' or [acute_id_r1] = '22', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -15839,12 +15839,12 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications] = '1' / If [acute_id_r2] = '9' or [acute_id_r2] = '18' or [acute_id_r2] = '20' or [acute_id_r2] = '22', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -16070,12 +16070,12 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications] = '1' / If [acute_id_r3] = '9' or [acute_id_r3] = '18' or [acute_id_r3] = '20' or [acute_id_r3] = '22', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -16301,12 +16301,12 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications] = '1' / If [acute_id_r4] = '9' or [acute_id_r4] = '18' or [acute_id_r4] = '20' or [acute_id_r4] = '22', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -16635,12 +16635,12 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r2] = '25' or [acute_id_scd_r2] = '27' or [acute_id_scd_r2] = '35' or [acute_id_scd_r2] = '42', or [acute_id_scd_r2] = '44', or [acute_id_scd_r2] = '45', or [acute_id_scd_r2] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r3] = '25' or [acute_id_scd_r3] = '27' or [acute_id_scd_r3] = '35' or [acute_id_scd_r3] = '42', or [acute_id_scd_r3] = '44', or [acute_id_scd_r3] = '45', or [acute_id_scd_r3] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -17105,12 +17105,12 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r4] = '25' or [acute_id_scd_r4] = '27' or [acute_id_scd_r4] = '35' or [acute_id_scd_r4] = '42', or [acute_id_scd_r4] = '44', or [acute_id_scd_r4] = '45', or [acute_id_scd_r4] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -17340,12 +17340,12 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r5] = '25' or [acute_id_scd_r5] = '27' or [acute_id_scd_r5] = '35' or [acute_id_scd_r5] = '42', or [acute_id_scd_r5] = '44', or [acute_id_scd_r5] = '45', or [acute_id_scd_r5] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -17575,12 +17575,12 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r6] = '25' or [acute_id_scd_r6] = '27' or [acute_id_scd_r6] = '35' or [acute_id_scd_r6] = '42', or [acute_id_scd_r6] = '44', or [acute_id_scd_r6] = '45', or [acute_id_scd_r6] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -17810,12 +17810,12 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r7] = '25' or [acute_id_scd_r7] = '27' or [acute_id_scd_r7] = '35' or [acute_id_scd_r7] = '42', or [acute_id_scd_r7] = '44', or [acute_id_scd_r7] = '45', or [acute_id_scd_r7] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -18047,12 +18047,12 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r8] = '25' or [acute_id_scd_r8] = '27' or [acute_id_scd_r8] = '35' or [acute_id_scd_r8] = '42', or [acute_id_scd_r8] = '44', or [acute_id_scd_r8] = '45', or [acute_id_scd_r8] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -18282,12 +18282,12 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r9] = '25' or [acute_id_scd_r9] = '27' or [acute_id_scd_r9] = '35' or [acute_id_scd_r9] = '42', or [acute_id_scd_r9] = '44', or [acute_id_scd_r9] = '45', or [acute_id_scd_r9] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -18519,12 +18519,12 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r10] = '25' or [acute_id_scd_r10] = '27' or [acute_id_scd_r10] = '35' or [acute_id_scd_r10] = '42', or [acute_id_scd_r10] = '44', or [acute_id_scd_r10] = '45', or [acute_id_scd_r10] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -18754,12 +18754,12 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r11] = '25' or [acute_id_scd_r11] = '27' or [acute_id_scd_r11] = '35' or [acute_id_scd_r11] = '42', or [acute_id_scd_r11] = '44', or [acute_id_scd_r11] = '45', or [acute_id_scd_r11] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -18989,12 +18989,12 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r12] = '25' or [acute_id_scd_r12] = '27' or [acute_id_scd_r12] = '35' or [acute_id_scd_r12] = '42', or [acute_id_scd_r12] = '44', or [acute_id_scd_r12] = '45', or [acute_id_scd_r12] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -19224,12 +19224,12 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r13] = '25' or [acute_id_scd_r13] = '27' or [acute_id_scd_r13] = '35' or [acute_id_scd_r13] = '42', or [acute_id_scd_r13] = '44', or [acute_id_scd_r13] = '45', or [acute_id_scd_r13] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -19459,12 +19459,12 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r14] = '25' or [acute_id_scd_r14] = '27' or [acute_id_scd_r14] = '35' or [acute_id_scd_r14] = '42', or [acute_id_scd_r14] = '44', or [acute_id_scd_r14] = '45', or [acute_id_scd_r14] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -19694,12 +19694,12 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r15] = '25' or [acute_id_scd_r15] = '27' or [acute_id_scd_r15] = '35' or [acute_id_scd_r15] = '42', or [acute_id_scd_r15] = '44', or [acute_id_scd_r15] = '45', or [acute_id_scd_r15] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -19929,12 +19929,12 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Cannot be empty if [acute_complications_scd] = '1' / Date range must be between [birth_date] and [death_date] or [episode_date]</t>
+          <t>Cannot be empty if [acute_complications_scd] = '1' / If [acute_id_scd_r16] = '25' or [acute_id_scd_r16] = '27' or [acute_id_scd_r16] = '35' or [acute_id_scd_r16] = '42', or [acute_id_scd_r16] = '44', or [acute_id_scd_r16] = '45', or [acute_id_scd_r16] = '46', date range must be between [episode_date] - 2 years and [episode_date]. If not, date range must be between [birth_date] and [death_date] or [episode_date]</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>[date_of_birth]</t>
+          <t>if [current-instance] &gt; '1', [timestamp] - 2 years. Else, [date_of_birth]</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
